--- a/notebooks/results/excel/scotland/Q3_reduced_scotland_tot=4_flex=0.1_xcfe=3.xlsx
+++ b/notebooks/results/excel/scotland/Q3_reduced_scotland_tot=4_flex=0.1_xcfe=3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marta/Documents/MSc CAM/Dissertation/PyPSA-GB/notebooks/results/excel/scotland/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C3E5A5-2CF0-D741-821F-C24B20597EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807A19AB-640E-0D4E-BCD5-1E2CF9352F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9080" yWindow="660" windowWidth="19880" windowHeight="17400" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
+    <workbookView minimized="1" xWindow="-20" yWindow="680" windowWidth="15140" windowHeight="17400" xr2:uid="{D4188A73-9F76-7B43-A2AE-82D891E862BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="8" r:id="rId1"/>
@@ -525,6 +525,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -534,8 +536,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1150,168 +1150,156 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="21">
         <f ca="1">1-C$11/$B$11</f>
         <v>2.3948960529447394E-3</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="21">
         <f t="shared" ref="D18:G18" ca="1" si="5">1-D$11/$B$11</f>
         <v>-1.9217052012992619E-2</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="21">
         <f t="shared" ca="1" si="5"/>
         <v>-2.5685716192343166E-2</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="21">
         <f t="shared" ca="1" si="5"/>
         <v>5.8806188550472038E-3</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="21">
         <f t="shared" ca="1" si="5"/>
         <v>-1.6458657743755323E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="21">
         <f ca="1">1-C$12/$B$12</f>
         <v>3.9993730842673436E-3</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="21">
         <f t="shared" ref="D19:G19" ca="1" si="6">1-D$12/$B$12</f>
         <v>-4.3470674149707955E-2</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="21">
         <f t="shared" ca="1" si="6"/>
         <v>-2.6319771287169003E-2</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="21">
         <f t="shared" ca="1" si="6"/>
         <v>1.5502764888082332E-3</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="21">
         <f t="shared" ca="1" si="6"/>
         <v>-1.8272094375810122E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="21">
         <f ca="1">1-C$13/$B$13</f>
         <v>7.163592668179819E-2</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="21">
         <f t="shared" ref="D20:G20" ca="1" si="7">1-D$13/$B$13</f>
         <v>2.5921086930261295E-2</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="21">
         <f t="shared" ca="1" si="7"/>
         <v>-7.3715564541252387E-3</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="21">
         <f t="shared" ca="1" si="7"/>
         <v>4.121701094178154E-2</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="21">
         <f t="shared" ca="1" si="7"/>
         <v>2.3468245945310162E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="21">
         <f ca="1">1-C$14/$B$14</f>
         <v>-0.1649894665005045</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="21">
         <f t="shared" ref="D21:G21" ca="1" si="8">1-D$14/$B$14</f>
         <v>2.909322888849375E-3</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="21">
         <f t="shared" ca="1" si="8"/>
         <v>-4.7744940953059256E-2</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="21">
         <f t="shared" ca="1" si="8"/>
         <v>-4.9566049492611786E-2</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="21">
         <f t="shared" ca="1" si="8"/>
         <v>-8.5207851166102966E-2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="21">
         <f ca="1">1-C$15/$B$15</f>
         <v>1.4901968561379375E-3</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="21">
         <f t="shared" ref="D22:G22" ca="1" si="9">1-D$15/$B$15</f>
         <v>-4.0725436895394651E-4</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="21">
         <f t="shared" ca="1" si="9"/>
         <v>2.7367493593711822E-3</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="21">
         <f t="shared" ca="1" si="9"/>
         <v>0</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="21">
         <f t="shared" ca="1" si="9"/>
         <v>1.0836507556516328E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="21">
         <f>1-C$16/$B$16</f>
         <v>4.5678710174917869E-3</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="21">
         <f t="shared" ref="D23:G23" si="10">1-D$16/$B$16</f>
         <v>2.2508183450626884E-3</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="21">
         <f t="shared" si="10"/>
         <v>6.8191787800838677E-3</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="21">
         <f t="shared" si="10"/>
         <v>-7.3274719625260332E-15</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="21">
         <f t="shared" si="10"/>
         <v>1.6958000880951563E-2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C18:G23">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B11:G11">
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -1384,6 +1372,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G23">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1440,7 +1440,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -1484,7 +1484,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -1526,7 +1526,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -1568,7 +1568,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -1610,7 +1610,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -1652,7 +1652,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -1736,7 +1736,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -1778,7 +1778,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -1820,7 +1820,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -1862,7 +1862,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -1904,7 +1904,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -1946,7 +1946,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -1988,7 +1988,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -2030,7 +2030,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -2072,7 +2072,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -2114,7 +2114,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -2156,7 +2156,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -2198,7 +2198,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -2240,7 +2240,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -2370,7 +2370,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>41</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="15" t="s">
         <v>40</v>
       </c>
@@ -2454,7 +2454,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -2498,7 +2498,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="15" t="s">
         <v>37</v>
       </c>
@@ -2540,7 +2540,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -2584,7 +2584,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="15" t="s">
         <v>34</v>
       </c>
@@ -2626,7 +2626,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>33</v>
       </c>
@@ -2668,7 +2668,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="15" t="s">
         <v>32</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -2953,7 +2953,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -2995,7 +2995,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -3037,7 +3037,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -3079,7 +3079,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -3163,7 +3163,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -3205,7 +3205,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -3247,7 +3247,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -3289,7 +3289,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -3331,7 +3331,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -3373,7 +3373,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -3415,7 +3415,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -3457,7 +3457,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -3499,7 +3499,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -3541,7 +3541,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -3583,7 +3583,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -3625,7 +3625,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -3709,7 +3709,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -3795,7 +3795,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -3839,7 +3839,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>79</v>
       </c>
@@ -3881,7 +3881,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="15" t="s">
         <v>41</v>
       </c>
@@ -3923,7 +3923,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="15" t="s">
         <v>40</v>
       </c>
@@ -3965,7 +3965,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -4009,7 +4009,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="15" t="s">
         <v>37</v>
       </c>
@@ -4051,7 +4051,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -4095,7 +4095,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>34</v>
       </c>
@@ -4137,7 +4137,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>33</v>
       </c>
@@ -4179,7 +4179,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="15" t="s">
         <v>32</v>
       </c>
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B33" s="15" t="s">
@@ -4265,7 +4265,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
+      <c r="A34" s="24"/>
       <c r="B34" s="15" t="s">
         <v>30</v>
       </c>
@@ -4453,7 +4453,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -4497,7 +4497,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -4539,7 +4539,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -4581,7 +4581,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -4623,7 +4623,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -4665,7 +4665,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -4707,7 +4707,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -4749,7 +4749,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -4791,7 +4791,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -4833,7 +4833,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -4875,7 +4875,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -4917,7 +4917,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -4959,7 +4959,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -5001,7 +5001,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -5043,7 +5043,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -5085,7 +5085,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -5127,7 +5127,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -5169,7 +5169,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -5211,7 +5211,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -5253,7 +5253,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -5339,7 +5339,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -5383,7 +5383,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>41</v>
       </c>
@@ -5425,7 +5425,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="15" t="s">
         <v>40</v>
       </c>
@@ -5467,7 +5467,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="22"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="15" t="s">
         <v>80</v>
       </c>
@@ -5509,7 +5509,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="15" t="s">
@@ -5553,7 +5553,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="22"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="15" t="s">
         <v>37</v>
       </c>
@@ -5595,7 +5595,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -5639,7 +5639,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>34</v>
       </c>
@@ -5681,7 +5681,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>33</v>
       </c>
@@ -5723,7 +5723,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="15" t="s">
         <v>32</v>
       </c>
@@ -5955,7 +5955,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -5999,7 +5999,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -6041,7 +6041,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -6083,7 +6083,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -6125,7 +6125,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -6167,7 +6167,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -6209,7 +6209,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -6251,7 +6251,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -6293,7 +6293,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -6335,7 +6335,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -6377,7 +6377,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -6419,7 +6419,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -6461,7 +6461,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -6503,7 +6503,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -6545,7 +6545,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -6587,7 +6587,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -6629,7 +6629,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -6671,7 +6671,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -6713,7 +6713,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -6755,7 +6755,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -6841,7 +6841,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -6885,7 +6885,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>79</v>
       </c>
@@ -6927,7 +6927,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="15" t="s">
         <v>41</v>
       </c>
@@ -6969,7 +6969,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="23"/>
       <c r="B26" s="15" t="s">
         <v>40</v>
       </c>
@@ -7011,7 +7011,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="15" t="s">
         <v>80</v>
       </c>
@@ -7053,7 +7053,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -7097,7 +7097,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="15" t="s">
         <v>37</v>
       </c>
@@ -7139,7 +7139,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="15" t="s">
@@ -7183,7 +7183,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>34</v>
       </c>
@@ -7225,7 +7225,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="15" t="s">
         <v>33</v>
       </c>
@@ -7267,7 +7267,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
@@ -7309,7 +7309,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -7353,7 +7353,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="15" t="s">
         <v>30</v>
       </c>
@@ -7544,7 +7544,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -7588,7 +7588,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -7630,7 +7630,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -7672,7 +7672,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -7714,7 +7714,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -7756,7 +7756,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -7798,7 +7798,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -7840,7 +7840,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -7882,7 +7882,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -7924,7 +7924,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -7966,7 +7966,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -8008,7 +8008,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -8050,7 +8050,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -8092,7 +8092,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -8134,7 +8134,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -8176,7 +8176,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -8218,7 +8218,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -8260,7 +8260,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -8302,7 +8302,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -8344,7 +8344,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -8430,7 +8430,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -8474,7 +8474,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>41</v>
       </c>
@@ -8516,7 +8516,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="22"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="15" t="s">
         <v>40</v>
       </c>
@@ -8558,7 +8558,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -8602,7 +8602,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="15" t="s">
         <v>37</v>
       </c>
@@ -8644,7 +8644,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -8688,7 +8688,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="15" t="s">
         <v>34</v>
       </c>
@@ -8730,7 +8730,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>33</v>
       </c>
@@ -8772,7 +8772,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="22"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="15" t="s">
         <v>32</v>
       </c>
@@ -8996,7 +8996,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="15" t="s">
@@ -9040,7 +9040,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="15" t="s">
         <v>64</v>
       </c>
@@ -9082,7 +9082,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="15" t="s">
         <v>63</v>
       </c>
@@ -9124,7 +9124,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
@@ -9166,7 +9166,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="21"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>61</v>
       </c>
@@ -9208,7 +9208,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>60</v>
       </c>
@@ -9250,7 +9250,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>59</v>
       </c>
@@ -9292,7 +9292,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>58</v>
       </c>
@@ -9334,7 +9334,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>57</v>
       </c>
@@ -9376,7 +9376,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -9418,7 +9418,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>55</v>
       </c>
@@ -9460,7 +9460,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15" t="s">
         <v>54</v>
       </c>
@@ -9502,7 +9502,7 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="15" t="s">
         <v>53</v>
       </c>
@@ -9544,7 +9544,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
@@ -9586,7 +9586,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="15" t="s">
         <v>51</v>
       </c>
@@ -9628,7 +9628,7 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
@@ -9670,7 +9670,7 @@
       </c>
     </row>
     <row r="18" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>49</v>
       </c>
@@ -9712,7 +9712,7 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
       </c>
@@ -9754,7 +9754,7 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>47</v>
       </c>
@@ -9796,7 +9796,7 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="15" t="s">
         <v>46</v>
       </c>
@@ -9882,7 +9882,7 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="22" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="15" t="s">
@@ -9926,7 +9926,7 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="15" t="s">
         <v>79</v>
       </c>
@@ -9968,7 +9968,7 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="15" t="s">
         <v>41</v>
       </c>
@@ -10010,7 +10010,7 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="23"/>
       <c r="B26" s="15" t="s">
         <v>40</v>
       </c>
@@ -10052,7 +10052,7 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="15" t="s">
         <v>80</v>
       </c>
@@ -10094,7 +10094,7 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="22" t="s">
         <v>39</v>
       </c>
       <c r="B28" s="15" t="s">
@@ -10138,7 +10138,7 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="15" t="s">
         <v>37</v>
       </c>
@@ -10180,7 +10180,7 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="15" t="s">
@@ -10224,7 +10224,7 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>34</v>
       </c>
@@ -10266,7 +10266,7 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="15" t="s">
         <v>33</v>
       </c>
@@ -10308,7 +10308,7 @@
       </c>
     </row>
     <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="22"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="15" t="s">
         <v>32</v>
       </c>
@@ -10350,7 +10350,7 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>31</v>
       </c>
       <c r="B34" s="15" t="s">
@@ -10394,7 +10394,7 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="22"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="15" t="s">
         <v>30</v>
       </c>
